--- a/data/13April-Oaks-v-Razorbacks.xlsx
+++ b/data/13April-Oaks-v-Razorbacks.xlsx
@@ -322,7 +322,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:O160"/>
   <sheetData>
     <row r="1">
@@ -1388,8 +1388,10 @@
       <c r="D109" t="s">
         <v>42</v>
       </c>
-      <c r="E109" t="s">
-        <v>60</v>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>UCDC</t>
+        </is>
       </c>
       <c r="J109" t="s">
         <v>61</v>
@@ -1419,8 +1421,10 @@
       <c r="D111" t="s">
         <v>42</v>
       </c>
-      <c r="E111" t="s">
-        <v>64</v>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>LCDN</t>
+        </is>
       </c>
       <c r="F111" t="s">
         <v>65</v>
@@ -1491,8 +1495,10 @@
       <c r="D117" t="s">
         <v>42</v>
       </c>
-      <c r="E117" t="s">
-        <v>69</v>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
       </c>
       <c r="J117" t="s">
         <v>50</v>
@@ -1551,8 +1557,10 @@
       <c r="D123" t="s">
         <v>42</v>
       </c>
-      <c r="E123" t="s">
-        <v>69</v>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
       </c>
       <c r="J123" t="s">
         <v>70</v>
